--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486488_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486488_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6031</v>
+        <v>4.3055</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5059</v>
+        <v>3.2391</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0972</v>
+        <v>1.0664</v>
       </c>
       <c r="G2" t="n">
         <v>5.0262</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0119</v>
+        <v>-0.2857</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2091</v>
+        <v>-0.0577</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1972</v>
+        <v>-0.228</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2461</v>
+        <v>2.7579</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0671</v>
+        <v>3.9179</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.821</v>
+        <v>-1.16</v>
       </c>
       <c r="G3" t="n">
         <v>3.5577</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7211</v>
+        <v>-0.2094</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1524</v>
+        <v>-0.3016</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4313</v>
+        <v>0.0922</v>
       </c>
       <c r="V3" t="n">
         <v>-1.243</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4205</v>
+        <v>2.4917</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4145</v>
+        <v>3.085</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.994</v>
+        <v>-0.5933</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2623</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9644</v>
+        <v>-0.8932</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2209</v>
+        <v>-0.5504</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7435</v>
+        <v>-0.3428</v>
       </c>
       <c r="V4" t="n">
         <v>2.3422</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. TABOADA HEISKANEN</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9716</v>
+        <v>1.2756</v>
       </c>
       <c r="E5" t="n">
-        <v>1.516</v>
+        <v>-1.4161</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5444</v>
+        <v>2.6917</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2745</v>
+        <v>1.8434</v>
       </c>
       <c r="H5" t="n">
-        <v>0.657</v>
+        <v>3.6435</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3825</v>
+        <v>-1.8001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8395</v>
+        <v>0.9566</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8395</v>
+        <v>3.2484</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-2.2917</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.8868</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1825</v>
+        <v>0.3951</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3825</v>
+        <v>0.4916</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6971000000000001</v>
+        <v>-0.5456</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6766</v>
+        <v>-0.3929</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0205</v>
+        <v>-0.1526</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>C. TABOADA HEISKANEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8603</v>
+        <v>0.5554</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7082</v>
+        <v>1.069</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5684</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8434</v>
+        <v>0.2745</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6435</v>
+        <v>0.657</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8001</v>
+        <v>-0.3825</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9566</v>
+        <v>0.8395</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2484</v>
+        <v>0.8395</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2917</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8868</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3951</v>
+        <v>-0.1825</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4916</v>
+        <v>-0.3825</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9609</v>
+        <v>0.2809</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.2295</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2759</v>
+        <v>0.0514</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4373</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1463</v>
+        <v>-1.2348</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5836</v>
+        <v>0.4491</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1798</v>
+        <v>-1.3591</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6601</v>
+        <v>-1.1559</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5196</v>
+        <v>-0.2032</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3218</v>
+        <v>-1.1199</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9520999999999999</v>
+        <v>-0.4896</v>
       </c>
       <c r="L7" t="n">
         <v>-0.6303</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5016</v>
+        <v>-0.2392</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6123</v>
+        <v>-0.6663</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8893</v>
+        <v>0.4271</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2247</v>
+        <v>-0.5789</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9337</v>
+        <v>-0.1574</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2909</v>
+        <v>-0.4215</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2223</v>
+        <v>0.9347</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.1093</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.113</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1472</v>
+        <v>-1.4123</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7504</v>
+        <v>-0.8595</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6032</v>
+        <v>-0.5528</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3591</v>
+        <v>-2.1798</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1559</v>
+        <v>-0.6601</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2032</v>
+        <v>-1.5196</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1199</v>
+        <v>0.3218</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4896</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6303</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2392</v>
+        <v>-2.5016</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6663</v>
+        <v>-1.6123</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4271</v>
+        <v>-0.8893</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9403</v>
+        <v>0.2497</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.0721</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2674</v>
+        <v>0.3217</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9347</v>
+        <v>-1.2223</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>-1.1093</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.455</v>
+        <v>-1.5176</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3529</v>
+        <v>0.1979</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.808</v>
+        <v>-1.7155</v>
       </c>
       <c r="G9" t="n">
         <v>0.0788</v>
@@ -1156,13 +1156,13 @@
         <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0309</v>
+        <v>-0.0934</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0649</v>
+        <v>-0.2199</v>
       </c>
       <c r="U9" t="n">
-        <v>0.034</v>
+        <v>0.1265</v>
       </c>
       <c r="V9" t="n">
         <v>-2.3729</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9422</v>
+        <v>-2.0347</v>
       </c>
       <c r="E10" t="n">
         <v>-2.4086</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4664</v>
+        <v>0.3739</v>
       </c>
       <c r="G10" t="n">
         <v>-0.197</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0052</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>-0.137</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1318</v>
+        <v>0.0394</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5214</v>
+        <v>-2.6948</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0885</v>
+        <v>-1.2003</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4329</v>
+        <v>-1.4945</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9172</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0514</v>
+        <v>-0.122</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1454</v>
+        <v>-0.2572</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1968</v>
+        <v>0.1352</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4382</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.598500000000001</v>
+        <v>2.940900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.047000000000001</v>
+        <v>4.389600000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4487</v>
+        <v>-1.4486</v>
       </c>
       <c r="G12" t="n">
-        <v>5.8652</v>
+        <v>5.865199999999999</v>
       </c>
       <c r="H12" t="n">
         <v>11.6027</v>
@@ -1390,19 +1390,19 @@
         <v>13.0505</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6377</v>
+        <v>-2.2952</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2591</v>
+        <v>-1.9167</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3787</v>
+        <v>-0.3784999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8043</v>
       </c>
       <c r="W12" t="n">
-        <v>4.756500000000001</v>
+        <v>4.7565</v>
       </c>
       <c r="X12" t="n">
         <v>-7.560700000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4683</v>
+        <v>6.0335</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2318</v>
+        <v>4.6788</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2365</v>
+        <v>1.3547</v>
       </c>
       <c r="G13" t="n">
         <v>4.4062</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1729</v>
+        <v>0.7381</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2019</v>
+        <v>0.2452</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3748</v>
+        <v>0.493</v>
       </c>
       <c r="V13" t="n">
         <v>3.9342</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0012</v>
+        <v>2.7431</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6586</v>
+        <v>0.7703</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3426</v>
+        <v>1.9727</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7983</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9539</v>
+        <v>0.6958</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1334</v>
+        <v>-0.0216</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0873</v>
+        <v>0.7174</v>
       </c>
       <c r="V14" t="n">
         <v>2.8456</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2294</v>
+        <v>0.9333</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1657</v>
+        <v>-0.0636</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0637</v>
+        <v>0.9969</v>
       </c>
       <c r="G15" t="n">
         <v>0.7702</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5468</v>
+        <v>1.2507</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9528</v>
+        <v>0.7234</v>
       </c>
       <c r="U15" t="n">
-        <v>0.594</v>
+        <v>0.5272</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2559</v>
+        <v>0.1397</v>
       </c>
       <c r="E16" t="n">
         <v>1.1818</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4376</v>
+        <v>-1.042</v>
       </c>
       <c r="G16" t="n">
         <v>0.4904</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.291</v>
+        <v>0.1046</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0769</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2141</v>
+        <v>0.1815</v>
       </c>
       <c r="V16" t="n">
         <v>-1.3252</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2757</v>
+        <v>-0.083</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3847</v>
+        <v>-0.1612</v>
       </c>
       <c r="F17" t="n">
-        <v>0.109</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7707000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1575</v>
+        <v>0.0352</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3219</v>
+        <v>0.2911</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3161</v>
+        <v>-1.1735</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0249</v>
+        <v>0.4473</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.341</v>
+        <v>-1.6208</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4871</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2038</v>
+        <v>-1.9006</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6909</v>
+        <v>1.012</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0523</v>
+        <v>0.664</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9376</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1147</v>
+        <v>-0.2246</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5652</v>
+        <v>-1.5526</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1414</v>
+        <v>-2.7893</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5760999999999999</v>
+        <v>1.2367</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0875</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2397</v>
+        <v>-0.1974</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0601</v>
+        <v>-0.3016</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1796</v>
+        <v>0.1042</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9554</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9554</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2332</v>
+        <v>-1.3212</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3351</v>
+        <v>1.0249</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8982</v>
+        <v>-2.3461</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8885999999999999</v>
+        <v>0.4871</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9006</v>
+        <v>-0.2038</v>
       </c>
       <c r="I19" t="n">
-        <v>1.012</v>
+        <v>0.6909</v>
       </c>
       <c r="J19" t="n">
-        <v>0.664</v>
+        <v>2.0523</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.9376</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2246</v>
+        <v>0.1147</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5526</v>
+        <v>-1.5652</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.7893</v>
+        <v>-2.1414</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2367</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2571</v>
+        <v>0.2346</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0839</v>
+        <v>0.0601</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1732</v>
+        <v>0.1745</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.9554</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.695</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6371</v>
+        <v>-2.3418</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8551</v>
+        <v>-2.0786</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7821</v>
+        <v>-0.2632</v>
       </c>
       <c r="G20" t="n">
         <v>-4.2368</v>
@@ -2014,13 +2014,13 @@
         <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2947</v>
+        <v>0.59</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6802</v>
+        <v>0.4567</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3855</v>
+        <v>0.1334</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>C. BARTON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2495</v>
+        <v>-3.0445</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1429</v>
+        <v>-1.8729</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1066</v>
+        <v>-1.1716</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7618</v>
+        <v>-2.5629</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9458</v>
+        <v>-0.511</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.816</v>
+        <v>-2.0519</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2644</v>
+        <v>-1.5484</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1492</v>
+        <v>0.0365</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4136</v>
+        <v>-1.5849</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4974</v>
+        <v>-1.0144</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.095</v>
+        <v>-0.5475</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4024</v>
+        <v>-0.467</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6423</v>
+        <v>-0.2217</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2091</v>
+        <v>-0.3245</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4332</v>
+        <v>0.1027</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. BARTON</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3297</v>
+        <v>-3.7389</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0964</v>
+        <v>-2.4782</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2333</v>
+        <v>-1.2607</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5629</v>
+        <v>-2.7618</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.511</v>
+        <v>-0.9458</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0519</v>
+        <v>-1.816</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5484</v>
+        <v>-1.2644</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0365</v>
+        <v>0.1492</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5849</v>
+        <v>-1.4136</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0144</v>
+        <v>-1.4974</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5475</v>
+        <v>-1.095</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.467</v>
+        <v>-0.4024</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5069</v>
+        <v>0.1529</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.548</v>
+        <v>-0.1262</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0411</v>
+        <v>0.2791</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5983</v>
+        <v>-1.8533</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4486</v>
+        <v>1.448599999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.047</v>
+        <v>-3.3019</v>
       </c>
       <c r="G23" t="n">
         <v>-5.8652</v>
@@ -2248,13 +2248,13 @@
         <v>10.8751</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6378</v>
+        <v>3.3828</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3786</v>
+        <v>0.3786000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2591</v>
+        <v>3.0041</v>
       </c>
       <c r="V23" t="n">
         <v>2.8042</v>
